--- a/meta/dist/20261030_Meta個股模型_v0.1.1.xlsx
+++ b/meta/dist/20261030_Meta個股模型_v0.1.1.xlsx
@@ -14522,7 +14522,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">13 </t>
+      <t xml:space="preserve">12 </t>
     </r>
     <r>
       <rPr>
@@ -20347,7 +20347,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">51 </t>
+      <t xml:space="preserve">51</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">58 </t>
     </r>
     <r>
       <rPr>
